--- a/Structure/zh-CN/bom表.xlsx
+++ b/Structure/zh-CN/bom表.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\林鼎\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FINS实验室\FinsROV-An-Underwater-Camera-Based-Multi-Robot-Platform\Structure\zh-CN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CF3D104-918A-46B5-B2D4-48BCC0DE474D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23E3A8FE-2586-44D0-8AC1-663675A37C78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{880EE660-C71F-4428-A3AE-46F35EABC731}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="108">
   <si>
     <t>材料名</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -173,10 +173,6 @@
     <t>https://item.taobao.com/item.htm?spm=a1z09.2.0.0.ef7d2e8dO2XjuV&amp;id=662343463249&amp;_u=92ig9se46f55</t>
   </si>
   <si>
-    <t>舱管和法兰套装+
-半球罩+压板</t>
-  </si>
-  <si>
     <t>C板</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -394,11 +390,23 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>50m零浮力线缆+外置相机预计总价10000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>可以将电缆直接寄给商家加工</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>算上50m零浮力线缆+外置相机，预计总价10000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>前舱盖/半球罩</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>舱管和法兰套装</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>无孔铝合金舱盖/半球罩+压板</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -507,7 +515,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="26">
+  <borders count="27">
     <border>
       <left/>
       <right/>
@@ -828,6 +836,15 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFDEE0E3"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -837,7 +854,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -946,61 +963,76 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1318,7 +1350,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF5F93B5-D5CA-4980-846C-F464AC4EE1A8}">
-  <dimension ref="A1:L32"/>
+  <dimension ref="A1:L33"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="13.08203125" bestFit="1" customWidth="1"/>
@@ -1347,26 +1379,26 @@
         <v>4</v>
       </c>
       <c r="F1" s="23" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G1" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="52" t="s">
+      <c r="I1" s="46" t="s">
+        <v>88</v>
+      </c>
+      <c r="J1" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="J1" s="12" t="s">
-        <v>90</v>
-      </c>
       <c r="K1" s="13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L1" s="14" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="50" t="s">
+      <c r="A2" s="53" t="s">
         <v>33</v>
       </c>
       <c r="B2" s="15" t="s">
@@ -1378,24 +1410,24 @@
       <c r="D2" s="15">
         <v>240</v>
       </c>
-      <c r="E2" s="47" t="s">
-        <v>44</v>
+      <c r="E2" s="50" t="s">
+        <v>43</v>
       </c>
       <c r="F2" s="16"/>
       <c r="G2" s="17"/>
-      <c r="I2" s="52"/>
-      <c r="J2" s="40" t="s">
+      <c r="I2" s="46"/>
+      <c r="J2" s="42" t="s">
+        <v>62</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>63</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>64</v>
       </c>
       <c r="L2" s="33">
         <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="51"/>
+      <c r="A3" s="54"/>
       <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
@@ -1405,20 +1437,20 @@
       <c r="D3" s="2">
         <v>180</v>
       </c>
-      <c r="E3" s="48"/>
+      <c r="E3" s="51"/>
       <c r="F3" s="3"/>
       <c r="G3" s="4"/>
-      <c r="I3" s="52"/>
-      <c r="J3" s="40"/>
+      <c r="I3" s="46"/>
+      <c r="J3" s="42"/>
       <c r="K3" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="L3" s="29">
         <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="51"/>
+      <c r="A4" s="54"/>
       <c r="B4" s="2" t="s">
         <v>8</v>
       </c>
@@ -1428,20 +1460,20 @@
       <c r="D4" s="2">
         <v>680</v>
       </c>
-      <c r="E4" s="48"/>
+      <c r="E4" s="51"/>
       <c r="F4" s="3"/>
       <c r="G4" s="4"/>
-      <c r="I4" s="52"/>
-      <c r="J4" s="41"/>
+      <c r="I4" s="46"/>
+      <c r="J4" s="43"/>
       <c r="K4" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="L4" s="29">
         <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="51"/>
+      <c r="A5" s="54"/>
       <c r="B5" s="2" t="s">
         <v>9</v>
       </c>
@@ -1451,21 +1483,21 @@
       <c r="D5" s="2">
         <v>480</v>
       </c>
-      <c r="E5" s="48"/>
+      <c r="E5" s="51"/>
       <c r="F5" s="3"/>
       <c r="G5" s="4"/>
-      <c r="J5" s="42" t="s">
+      <c r="J5" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="K5" s="2" t="s">
         <v>67</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>68</v>
       </c>
       <c r="L5" s="29">
         <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="51"/>
+      <c r="A6" s="54"/>
       <c r="B6" s="2" t="s">
         <v>10</v>
       </c>
@@ -1475,21 +1507,21 @@
       <c r="D6" s="2">
         <v>1140</v>
       </c>
-      <c r="E6" s="49"/>
+      <c r="E6" s="52"/>
       <c r="F6" s="3"/>
       <c r="G6" s="4"/>
-      <c r="J6" s="40"/>
+      <c r="J6" s="42"/>
       <c r="K6" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="L6" s="29">
         <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="28" x14ac:dyDescent="0.3">
-      <c r="A7" s="51"/>
+      <c r="A7" s="54"/>
       <c r="B7" s="9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C7" s="2">
         <v>1</v>
@@ -1498,25 +1530,25 @@
         <v>272</v>
       </c>
       <c r="E7" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="F7" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="G7" s="54" t="s">
-        <v>105</v>
-      </c>
-      <c r="J7" s="40"/>
+      <c r="G7" s="36" t="s">
+        <v>103</v>
+      </c>
+      <c r="J7" s="42"/>
       <c r="K7" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L7" s="29">
         <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="26" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="51"/>
-      <c r="B8" s="44" t="s">
+      <c r="A8" s="54"/>
+      <c r="B8" s="47" t="s">
         <v>18</v>
       </c>
       <c r="C8" s="2">
@@ -1532,17 +1564,17 @@
         <v>20</v>
       </c>
       <c r="G8" s="10"/>
-      <c r="J8" s="40"/>
+      <c r="J8" s="42"/>
       <c r="K8" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L8" s="29">
         <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="51"/>
-      <c r="B9" s="46"/>
+      <c r="A9" s="54"/>
+      <c r="B9" s="49"/>
       <c r="C9" s="2">
         <v>4</v>
       </c>
@@ -1554,16 +1586,16 @@
         <v>21</v>
       </c>
       <c r="G9" s="10"/>
-      <c r="J9" s="40"/>
+      <c r="J9" s="42"/>
       <c r="K9" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L9" s="29">
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="28" x14ac:dyDescent="0.3">
-      <c r="A10" s="51"/>
+    <row r="10" spans="1:12" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="54"/>
       <c r="B10" s="2" t="s">
         <v>38</v>
       </c>
@@ -1573,504 +1605,525 @@
       <c r="D10" s="2">
         <v>515</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="58" t="s">
         <v>39</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>40</v>
+        <v>106</v>
       </c>
       <c r="G10" s="4"/>
-      <c r="J10" s="40"/>
+      <c r="J10" s="42"/>
       <c r="K10" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L10" s="29">
         <v>48</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" s="51"/>
-      <c r="B11" s="5" t="s">
+    <row r="11" spans="1:12" ht="26" x14ac:dyDescent="0.3">
+      <c r="A11" s="54"/>
+      <c r="B11" s="55" t="s">
+        <v>105</v>
+      </c>
+      <c r="C11" s="55">
+        <v>1</v>
+      </c>
+      <c r="D11" s="55">
+        <v>150</v>
+      </c>
+      <c r="E11" s="59"/>
+      <c r="F11" s="56" t="s">
+        <v>107</v>
+      </c>
+      <c r="G11" s="57"/>
+      <c r="J11" s="42"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="29"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A12" s="54"/>
+      <c r="B12" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="6" t="s">
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="F11" s="6"/>
-      <c r="G11" s="18"/>
-      <c r="J11" s="40"/>
-      <c r="K11" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="L11" s="29">
+      <c r="F12" s="6"/>
+      <c r="G12" s="18"/>
+      <c r="J12" s="42"/>
+      <c r="K12" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="L12" s="29">
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="28" x14ac:dyDescent="0.3">
-      <c r="A12" s="38" t="s">
+    <row r="13" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+      <c r="A13" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B13" s="2" t="s">
         <v>12</v>
-      </c>
-      <c r="C12" s="2">
-        <v>4</v>
-      </c>
-      <c r="D12" s="2">
-        <v>2037</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G12" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="J12" s="41"/>
-      <c r="K12" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="L12" s="29">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" ht="39" x14ac:dyDescent="0.3">
-      <c r="A13" s="38"/>
-      <c r="B13" s="2" t="s">
-        <v>15</v>
       </c>
       <c r="C13" s="2">
         <v>4</v>
       </c>
       <c r="D13" s="2">
-        <v>432</v>
+        <v>2037</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G13" s="18"/>
-      <c r="J13" s="42" t="s">
-        <v>76</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="J13" s="43"/>
       <c r="K13" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="L13" s="29">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" ht="52" x14ac:dyDescent="0.3">
-      <c r="A14" s="38"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="39" x14ac:dyDescent="0.3">
+      <c r="A14" s="40"/>
       <c r="B14" s="2" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C14" s="2">
         <v>4</v>
       </c>
       <c r="D14" s="2">
+        <v>432</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G14" s="18"/>
+      <c r="J14" s="44" t="s">
+        <v>75</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="L14" s="29">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="52" x14ac:dyDescent="0.3">
+      <c r="A15" s="40"/>
+      <c r="B15" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" s="2">
+        <v>4</v>
+      </c>
+      <c r="D15" s="2">
         <v>1319.6</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="E15" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="F14" s="11" t="s">
+      <c r="F15" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="G14" s="8" t="s">
+      <c r="G15" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="J14" s="41"/>
-      <c r="K14" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="L14" s="29">
+      <c r="J15" s="43"/>
+      <c r="K15" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="L15" s="29">
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15" s="38"/>
-      <c r="B15" s="2" t="s">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A16" s="40"/>
+      <c r="B16" s="2" t="s">
         <v>25</v>
-      </c>
-      <c r="C15" s="2">
-        <v>1</v>
-      </c>
-      <c r="D15" s="2">
-        <v>10.56</v>
-      </c>
-      <c r="E15" s="34" t="s">
-        <v>49</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="G15" s="4"/>
-      <c r="J15" s="42" t="s">
-        <v>79</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="L15" s="29">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" ht="28" x14ac:dyDescent="0.3">
-      <c r="A16" s="38"/>
-      <c r="B16" s="2" t="s">
-        <v>26</v>
       </c>
       <c r="C16" s="2">
         <v>1</v>
       </c>
       <c r="D16" s="2">
-        <v>15</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>27</v>
+        <v>10.56</v>
+      </c>
+      <c r="E16" s="34" t="s">
+        <v>48</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G16" s="10"/>
-      <c r="J16" s="40"/>
+        <v>49</v>
+      </c>
+      <c r="G16" s="4"/>
+      <c r="J16" s="44" t="s">
+        <v>78</v>
+      </c>
       <c r="K16" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="L16" s="29">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="28" x14ac:dyDescent="0.3">
-      <c r="A17" s="38"/>
+      <c r="A17" s="40"/>
       <c r="B17" s="2" t="s">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="C17" s="2">
         <v>1</v>
       </c>
       <c r="D17" s="2">
-        <v>9.1</v>
-      </c>
-      <c r="E17" s="34" t="s">
-        <v>53</v>
-      </c>
-      <c r="F17" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>28</v>
+      </c>
       <c r="G17" s="10"/>
-      <c r="J17" s="41"/>
+      <c r="J17" s="42"/>
       <c r="K17" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="L17" s="29">
         <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="28" x14ac:dyDescent="0.3">
-      <c r="A18" s="38"/>
+      <c r="A18" s="40"/>
       <c r="B18" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C18" s="2">
         <v>1</v>
       </c>
       <c r="D18" s="2">
+        <v>9.1</v>
+      </c>
+      <c r="E18" s="34" t="s">
+        <v>52</v>
+      </c>
+      <c r="F18" s="3"/>
+      <c r="G18" s="10"/>
+      <c r="J18" s="43"/>
+      <c r="K18" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="L18" s="29">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+      <c r="A19" s="40"/>
+      <c r="B19" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="2">
+        <v>1</v>
+      </c>
+      <c r="D19" s="2">
         <v>79</v>
       </c>
-      <c r="E18" s="34" t="s">
+      <c r="E19" s="34" t="s">
+        <v>54</v>
+      </c>
+      <c r="F19" s="3" t="s">
         <v>55</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="G18" s="10"/>
-      <c r="J18" s="30" t="s">
-        <v>83</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="L18" s="29">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" ht="28" x14ac:dyDescent="0.3">
-      <c r="A19" s="38"/>
-      <c r="B19" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C19" s="2">
-        <v>2</v>
-      </c>
-      <c r="D19" s="2">
-        <v>89</v>
-      </c>
-      <c r="E19" s="34" t="s">
-        <v>57</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>58</v>
       </c>
       <c r="G19" s="10"/>
       <c r="J19" s="30" t="s">
+        <v>82</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="L19" s="29">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+      <c r="A20" s="40"/>
+      <c r="B20" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C20" s="2">
+        <v>2</v>
+      </c>
+      <c r="D20" s="2">
+        <v>89</v>
+      </c>
+      <c r="E20" s="34" t="s">
+        <v>56</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G20" s="10"/>
+      <c r="J20" s="30" t="s">
+        <v>84</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="L20" s="29">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A21" s="40"/>
+      <c r="B21" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C21" s="2">
+        <v>1</v>
+      </c>
+      <c r="D21" s="2">
+        <v>379</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="F21" s="3"/>
+      <c r="G21" s="10"/>
+      <c r="J21" s="44" t="s">
         <v>85</v>
       </c>
-      <c r="K19" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="L19" s="29">
+      <c r="K21" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="L21" s="31">
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A20" s="38"/>
-      <c r="B20" s="2" t="s">
+    <row r="22" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+      <c r="A22" s="40"/>
+      <c r="B22" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C20" s="2">
+      <c r="C22" s="5">
         <v>1</v>
       </c>
-      <c r="D20" s="2">
-        <v>379</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="F20" s="3"/>
-      <c r="G20" s="10"/>
-      <c r="J20" s="42" t="s">
-        <v>86</v>
-      </c>
-      <c r="K20" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="L20" s="31">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" ht="28" x14ac:dyDescent="0.3">
-      <c r="A21" s="38"/>
-      <c r="B21" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C21" s="5">
-        <v>1</v>
-      </c>
-      <c r="D21" s="5"/>
-      <c r="F21" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="G21" s="19"/>
-      <c r="J21" s="40"/>
-      <c r="K21" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="L21" s="29">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" ht="42.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="38" t="s">
-        <v>34</v>
-      </c>
-      <c r="B22" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="C22" s="5"/>
       <c r="D22" s="5"/>
       <c r="F22" s="24" t="s">
-        <v>103</v>
+        <v>42</v>
       </c>
       <c r="G22" s="19"/>
-      <c r="J22" s="43"/>
-      <c r="K22" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="L22" s="32">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A23" s="38"/>
+      <c r="J22" s="42"/>
+      <c r="K22" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="L22" s="29">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="42.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="40" t="s">
+        <v>34</v>
+      </c>
       <c r="B23" s="9" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C23" s="5"/>
       <c r="D23" s="5"/>
       <c r="F23" s="24" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G23" s="19"/>
-    </row>
-    <row r="24" spans="1:12" ht="70" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="38"/>
-      <c r="B24" s="44" t="s">
-        <v>91</v>
-      </c>
-      <c r="C24" s="5">
-        <v>2</v>
-      </c>
-      <c r="D24" s="5">
-        <v>25.2</v>
-      </c>
-      <c r="E24" s="36" t="s">
-        <v>95</v>
-      </c>
+      <c r="J23" s="45"/>
+      <c r="K23" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="L23" s="32">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A24" s="40"/>
+      <c r="B24" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
       <c r="F24" s="24" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="G24" s="19"/>
     </row>
-    <row r="25" spans="1:12" ht="28" x14ac:dyDescent="0.3">
-      <c r="A25" s="38"/>
-      <c r="B25" s="45"/>
+    <row r="25" spans="1:12" ht="70" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="40"/>
+      <c r="B25" s="47" t="s">
+        <v>90</v>
+      </c>
       <c r="C25" s="5">
         <v>2</v>
       </c>
       <c r="D25" s="5">
-        <v>12.6</v>
-      </c>
-      <c r="E25" s="37"/>
+        <v>25.2</v>
+      </c>
+      <c r="E25" s="38" t="s">
+        <v>94</v>
+      </c>
       <c r="F25" s="24" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="G25" s="19"/>
     </row>
-    <row r="26" spans="1:12" ht="28" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="38"/>
-      <c r="B26" s="45"/>
+    <row r="26" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+      <c r="A26" s="40"/>
+      <c r="B26" s="48"/>
       <c r="C26" s="5">
         <v>2</v>
       </c>
       <c r="D26" s="5">
+        <v>12.6</v>
+      </c>
+      <c r="E26" s="39"/>
+      <c r="F26" s="24" t="s">
+        <v>99</v>
+      </c>
+      <c r="G26" s="19"/>
+    </row>
+    <row r="27" spans="1:12" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="40"/>
+      <c r="B27" s="48"/>
+      <c r="C27" s="5">
+        <v>2</v>
+      </c>
+      <c r="D27" s="5">
         <v>36</v>
       </c>
-      <c r="E26" s="36" t="s">
+      <c r="E27" s="38" t="s">
+        <v>96</v>
+      </c>
+      <c r="F27" s="24" t="s">
         <v>97</v>
       </c>
-      <c r="F26" s="24" t="s">
+      <c r="G27" s="19"/>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A28" s="40"/>
+      <c r="B28" s="49"/>
+      <c r="C28" s="5">
+        <v>1</v>
+      </c>
+      <c r="D28" s="5">
+        <v>24</v>
+      </c>
+      <c r="E28" s="39"/>
+      <c r="F28" s="24" t="s">
         <v>98</v>
       </c>
-      <c r="G26" s="19"/>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A27" s="38"/>
-      <c r="B27" s="46"/>
-      <c r="C27" s="5">
-        <v>1</v>
-      </c>
-      <c r="D27" s="5">
-        <v>24</v>
-      </c>
-      <c r="E27" s="37"/>
-      <c r="F27" s="24" t="s">
-        <v>99</v>
-      </c>
-      <c r="G27" s="19"/>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A28" s="38"/>
-      <c r="B28" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="C28" s="5"/>
-      <c r="D28" s="5"/>
-      <c r="F28" s="24"/>
       <c r="G28" s="19"/>
     </row>
-    <row r="29" spans="1:12" ht="42" x14ac:dyDescent="0.3">
-      <c r="A29" s="38"/>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A29" s="40"/>
       <c r="B29" s="9" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C29" s="5"/>
       <c r="D29" s="5"/>
-      <c r="F29" s="24" t="s">
-        <v>94</v>
-      </c>
+      <c r="F29" s="24"/>
       <c r="G29" s="19"/>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A30" s="38"/>
+    <row r="30" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+      <c r="A30" s="40"/>
       <c r="B30" s="9" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="C30" s="5"/>
       <c r="D30" s="5"/>
       <c r="F30" s="24" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="G30" s="19"/>
     </row>
-    <row r="31" spans="1:12" ht="28.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="39"/>
-      <c r="B31" s="20" t="s">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A31" s="40"/>
+      <c r="B31" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C31" s="5"/>
+      <c r="D31" s="5"/>
+      <c r="F31" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="G31" s="19"/>
+    </row>
+    <row r="32" spans="1:12" ht="28.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="41"/>
+      <c r="B32" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="C31" s="21">
+      <c r="C32" s="21">
         <v>12</v>
       </c>
-      <c r="D31" s="21"/>
-      <c r="E31" s="35" t="s">
+      <c r="D32" s="21"/>
+      <c r="E32" s="35" t="s">
+        <v>58</v>
+      </c>
+      <c r="F32" s="25" t="s">
         <v>59</v>
       </c>
-      <c r="F31" s="25" t="s">
-        <v>60</v>
-      </c>
-      <c r="G31" s="22"/>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A32" s="53" t="s">
+      <c r="G32" s="22"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33" s="37" t="s">
         <v>104</v>
       </c>
-      <c r="B32" s="53"/>
-      <c r="C32" s="53"/>
-      <c r="D32" s="53"/>
-      <c r="E32" s="53"/>
-      <c r="F32" s="53"/>
-      <c r="G32" s="53"/>
+      <c r="B33" s="37"/>
+      <c r="C33" s="37"/>
+      <c r="D33" s="37"/>
+      <c r="E33" s="37"/>
+      <c r="F33" s="37"/>
+      <c r="G33" s="37"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="A32:G32"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="A12:A21"/>
-    <mergeCell ref="A22:A31"/>
+  <mergeCells count="16">
+    <mergeCell ref="A33:G33"/>
+    <mergeCell ref="E27:E28"/>
+    <mergeCell ref="A13:A22"/>
+    <mergeCell ref="A23:A32"/>
     <mergeCell ref="J2:J4"/>
-    <mergeCell ref="J5:J12"/>
-    <mergeCell ref="J13:J14"/>
-    <mergeCell ref="J15:J17"/>
-    <mergeCell ref="J20:J22"/>
+    <mergeCell ref="J5:J13"/>
+    <mergeCell ref="J14:J15"/>
+    <mergeCell ref="J16:J18"/>
+    <mergeCell ref="J21:J23"/>
     <mergeCell ref="I1:I4"/>
-    <mergeCell ref="B24:B27"/>
-    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="B25:B28"/>
+    <mergeCell ref="E25:E26"/>
     <mergeCell ref="E2:E6"/>
     <mergeCell ref="B8:B9"/>
-    <mergeCell ref="A2:A11"/>
+    <mergeCell ref="A2:A12"/>
+    <mergeCell ref="E10:E11"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="E13" r:id="rId1" display="https://item.taobao.com/item.htm?_u=i20at7545jacc4&amp;id=680656749408&amp;spm=a1z09.2.0.0.3c6c2e8dmFwRSe" xr:uid="{3F73F5DD-3CDF-4863-AAEC-516705B41C0C}"/>
-    <hyperlink ref="E12" r:id="rId2" xr:uid="{673C0BF6-FA4B-4DD3-A524-AD8778BFF094}"/>
+    <hyperlink ref="E14" r:id="rId1" display="https://item.taobao.com/item.htm?_u=i20at7545jacc4&amp;id=680656749408&amp;spm=a1z09.2.0.0.3c6c2e8dmFwRSe" xr:uid="{3F73F5DD-3CDF-4863-AAEC-516705B41C0C}"/>
+    <hyperlink ref="E13" r:id="rId2" xr:uid="{673C0BF6-FA4B-4DD3-A524-AD8778BFF094}"/>
     <hyperlink ref="E8" r:id="rId3" xr:uid="{B716833D-E995-4E1A-BE25-1D1C237C45DB}"/>
-    <hyperlink ref="E14" r:id="rId4" display="https://item.taobao.com/item.htm?_u=320at7545j5b4a&amp;id=605375059849&amp;spm=a1z09.2.0.0.2d472e8d3f5Wg1" xr:uid="{C52128DF-CCEC-4082-AEC7-8424AA7D246D}"/>
-    <hyperlink ref="E16" r:id="rId5" display="https://detail.tmall.com/item.htm?_u=m20at7545j0770&amp;id=624960039615&amp;spm=a1z09.2.0.0.570d2e8dWadFaY" xr:uid="{50D5F49B-494F-44A2-9F2F-31D598AC82B9}"/>
-    <hyperlink ref="E20" r:id="rId6" display="https://item.taobao.com/item.htm?_u=i20at7545j5174&amp;id=611226266955&amp;spm=a1z09.2.0.0.292e2e8d43HZbM" xr:uid="{A7D1BC4F-6BA3-4A40-A9EB-12271480E3EF}"/>
+    <hyperlink ref="E15" r:id="rId4" display="https://item.taobao.com/item.htm?_u=320at7545j5b4a&amp;id=605375059849&amp;spm=a1z09.2.0.0.2d472e8d3f5Wg1" xr:uid="{C52128DF-CCEC-4082-AEC7-8424AA7D246D}"/>
+    <hyperlink ref="E17" r:id="rId5" display="https://detail.tmall.com/item.htm?_u=m20at7545j0770&amp;id=624960039615&amp;spm=a1z09.2.0.0.570d2e8dWadFaY" xr:uid="{50D5F49B-494F-44A2-9F2F-31D598AC82B9}"/>
+    <hyperlink ref="E21" r:id="rId6" display="https://item.taobao.com/item.htm?_u=i20at7545j5174&amp;id=611226266955&amp;spm=a1z09.2.0.0.292e2e8d43HZbM" xr:uid="{A7D1BC4F-6BA3-4A40-A9EB-12271480E3EF}"/>
     <hyperlink ref="E10" r:id="rId7" xr:uid="{F9F47241-9FCE-4980-9E52-E89C064A6868}"/>
     <hyperlink ref="E7" r:id="rId8" xr:uid="{C90F93AC-D989-4E2B-BB85-F11628D908B9}"/>
-    <hyperlink ref="E15" r:id="rId9" display="https://item.taobao.com/item.htm?id=677595693967&amp;pisk=gBYbOif88-2bGMbT1icPO0R9m8bsfbuEW519tCU46ZQAfPd2d1zNbmf_5TOKitoimdtWBLjVHOSN519FEIzZiIls5CddHN-V31pyCLq23FWwUVOHdiz26FPDqpRLuEoc7P_cSNHEL2uegIbGWb1xcOy0211Z7PCOXZb8LtNqv2ueiQNVMXR-8E7AmLf0XPpODgeRgTCOBPExNgCF6NUAXrE8eTXRWsQOHg3Ri65TXOpT28CdOSEA6oB-y61hWlpODQh5sTCOWNHAxJ5s_tOjiPG6Skg0ng67WPL5NAfvG5Ecp31b7OOVFc-6zswhpIB7WPB01tKpNIkb-Q7Dwp1e34UXdBYkF_pK5Y_MEhpO1L33QZxenejWZDUJaZ6lv6L-6yBwl3RdFwNtkQ_fhMLVDWzepQO9YgTr92bfktKNoCPI3QTX3IYW_5ERlZ-5AE_K--Bw4BT11FDiPpOHrL1JpVMA4I4FdsN7f7s35_6ENbZgj-kQ0QojXNAAD_ffPbG7haIAZ_6ENbZgjiClauGSN-_R.&amp;skuId=6126765579570&amp;spm=tbpc.boughtlist.suborder_itemtitle.1.67492e8dveCMAj" xr:uid="{76278D51-FE7D-40A4-AA86-CFB060BB6F93}"/>
-    <hyperlink ref="E17" r:id="rId10" display="https://detail.tmall.com/item.htm?_u=q2ig9se4d19b&amp;id=715839278393&amp;pisk=gJF0s8Geg-kfe-fhG3Gfp5m9KZWJljG__ldtXfnNU0o55KpAlAuaSlVTHPotslqgjmHNcjFgqyaOl5Qjg10avucTkmnTqNqY5CIfCjdwjoaFcrnOl5mZqoriCZitbcqT7-QR96UblfGZjMCd9M66kYrD3qkN70ux7a3VP-5aLfGNvGvJ_x1n1k6ed292U4oSSVJwgllr4V3t_Vuq_amrS29w0lraza0ISC-q7IJrU20q_nkquUorkVK2bmJq4a0t4hlZ_llrhmpsxoZLagy4L3E4QOwIoxmUumzY57RSLKaiq9W3Z8AmxrJ6_CPooxVO7Y7N-xeaRvNYg1ASMy2ra2UfiQcUu2qx2k5eZbz8zlHQFGOKFuVidSkX7aoziuVjgoBwtkc0jvPqEFRTubimZ4PFWpi8ZmEaiY7ptAhz9vl4eTsxBj03bSZDSCrUyyFjF5jH4cwxRbuLlsAoTruN4Y9yLT8X147Tad9s34govngwNZ0rJ_bGravCaxuSl_blrd9s34govabkLLkqPq1l.&amp;spm=a1z09.2.0.0.16022e8djmkhS9" xr:uid="{6FB9C11B-D844-4017-8FAE-7B9D33B02A74}"/>
-    <hyperlink ref="E18" r:id="rId11" display="https://detail.tmall.com/item.htm?abbucket=6&amp;id=599997955029&amp;pisk=g_FSJBgv_3x5MCbRv372fyTjpQGIVZ5aJegLSydyJbhJAvEafvPrayyBOkUTz0zUJ2FQYohEpgczOoZLAByzabkd9mZJTYPQ-BgLJkboYaX4rzcn9GSZO1zurRfUdZFSJqhYoVpJ2tkJDAvDLGSN_69vsmSCbz-EYGyx5VhKy0HJDZgISLhKe0dAl23e2Dn8vrQjm29pwXpJkK3K73hKyLCAM4uMyL3-9xCxm2hKvkhdljnmJXnLvXHpwhuC80a5RI-ZoeXt4znX9BFRtYisvpRBOS3SFWU-crz4G4MSXvZai2V80yFzZxj6XX44CkwLxOJmNye-wVzlNIGTy-PIuW7ed0EuGrFohFRZO8E7pA2fsdD-d0wYwxTp9rcxmAeQVg9o28rjIqHvR104bmUuw-_HDzEZVb3x31Q_kve4ZAVPDQGTIzlzpkXwnbaLejsz5Cos9NpBlAAIlc7flpvHQ1UCJ7KrBpk-o4GflZtSMY3mlc7flpvneq02hZ_XVjC..&amp;rn=617feaae5f94b5894f68d298b418e5fa&amp;spm=a1z10.5-b-s.w4011-25968523091.46.b6a0701d6EDwWY&amp;skuId=5973228525625" xr:uid="{E59FA095-5ED9-4AB6-A364-A1663E5F7967}"/>
-    <hyperlink ref="E19" r:id="rId12" display="https://item.taobao.com/item.htm?abbucket=8&amp;id=745548099223&amp;mi_id=00004OOG_NYymRcOUs8qQ4J16N7SfkKOrFY0K3XnxPj_dEs&amp;ns=1&amp;skuId=5310177214467&amp;spm=a21n57.1.hoverItem.2&amp;utparam=%7B%22aplus_abtest%22%3A%22d4a04f9cca5a6274e0629b42b0525f0d%22%7D&amp;xxc=taobaoSearch" xr:uid="{42F45CDB-86D2-44F7-A5BA-BEF4668BACD9}"/>
-    <hyperlink ref="E31" r:id="rId13" display="https://detail.tmall.com/item.htm?abbucket=6&amp;id=680012535670&amp;pisk=g0xjuU68YSVj0CDx6SkzOd_-JEI6lYoFMR69KdE4BiIxCcOWtNkDuou6PpASnGRwB1O6a_xqn1k01C96hZBABtn8e96b65E9BR69aiQMu15V1G9MOYlEYDJDnGbtTXoFPVtaTiBA6OQtBTBdQYWYJeyKYGjtTfazXZmCjIiagqyTyTClCoBAMCQ8wO1RHoB96_QRpOEAXGdtF_BchlEAXNe8e958W5IOXgQRLO4YWoItFLClBGC96ZHWe_XOX1H3EWWsQs9jCuy8KCoRDKC7XlKxjZ1Qe_BlU39lk6QRGlLyVt_f9KKKeo5Ve3-58ayZ-gpHzIB5A0zAvLT9Oedi8zjXBEdGPIcuP_8JmdCOzREeFp9vJgKZBJbWwO_dXawTXLscwN-AvDF5EUp2WnAbClBD0H71taMTjNSJYwLpGRDHeiB9swxZtofvBpxH8MizkMpWWBT14dEFOGHL58_3fT1EFYagSyopCAIABvhhkTXfVYM7GgQAET1EFYagSZBlUzMSFSsR.&amp;rn=231ec00e6e2790db3a6fd236d8bdbc94&amp;spm=a1z10.5-b.w4011-24399291437.54.78ac739ca5kPLK&amp;skuId=4875714089626" xr:uid="{58F62DF9-67CF-4905-8F70-77C15C8FD831}"/>
-    <hyperlink ref="E24" r:id="rId14" xr:uid="{EC25EA05-6DC9-4A87-9C36-32D903E88360}"/>
-    <hyperlink ref="E26" r:id="rId15" xr:uid="{2A053BBD-7322-4612-8A16-87449CD5652E}"/>
+    <hyperlink ref="E16" r:id="rId9" display="https://item.taobao.com/item.htm?id=677595693967&amp;pisk=gBYbOif88-2bGMbT1icPO0R9m8bsfbuEW519tCU46ZQAfPd2d1zNbmf_5TOKitoimdtWBLjVHOSN519FEIzZiIls5CddHN-V31pyCLq23FWwUVOHdiz26FPDqpRLuEoc7P_cSNHEL2uegIbGWb1xcOy0211Z7PCOXZb8LtNqv2ueiQNVMXR-8E7AmLf0XPpODgeRgTCOBPExNgCF6NUAXrE8eTXRWsQOHg3Ri65TXOpT28CdOSEA6oB-y61hWlpODQh5sTCOWNHAxJ5s_tOjiPG6Skg0ng67WPL5NAfvG5Ecp31b7OOVFc-6zswhpIB7WPB01tKpNIkb-Q7Dwp1e34UXdBYkF_pK5Y_MEhpO1L33QZxenejWZDUJaZ6lv6L-6yBwl3RdFwNtkQ_fhMLVDWzepQO9YgTr92bfktKNoCPI3QTX3IYW_5ERlZ-5AE_K--Bw4BT11FDiPpOHrL1JpVMA4I4FdsN7f7s35_6ENbZgj-kQ0QojXNAAD_ffPbG7haIAZ_6ENbZgjiClauGSN-_R.&amp;skuId=6126765579570&amp;spm=tbpc.boughtlist.suborder_itemtitle.1.67492e8dveCMAj" xr:uid="{76278D51-FE7D-40A4-AA86-CFB060BB6F93}"/>
+    <hyperlink ref="E18" r:id="rId10" display="https://detail.tmall.com/item.htm?_u=q2ig9se4d19b&amp;id=715839278393&amp;pisk=gJF0s8Geg-kfe-fhG3Gfp5m9KZWJljG__ldtXfnNU0o55KpAlAuaSlVTHPotslqgjmHNcjFgqyaOl5Qjg10avucTkmnTqNqY5CIfCjdwjoaFcrnOl5mZqoriCZitbcqT7-QR96UblfGZjMCd9M66kYrD3qkN70ux7a3VP-5aLfGNvGvJ_x1n1k6ed292U4oSSVJwgllr4V3t_Vuq_amrS29w0lraza0ISC-q7IJrU20q_nkquUorkVK2bmJq4a0t4hlZ_llrhmpsxoZLagy4L3E4QOwIoxmUumzY57RSLKaiq9W3Z8AmxrJ6_CPooxVO7Y7N-xeaRvNYg1ASMy2ra2UfiQcUu2qx2k5eZbz8zlHQFGOKFuVidSkX7aoziuVjgoBwtkc0jvPqEFRTubimZ4PFWpi8ZmEaiY7ptAhz9vl4eTsxBj03bSZDSCrUyyFjF5jH4cwxRbuLlsAoTruN4Y9yLT8X147Tad9s34govngwNZ0rJ_bGravCaxuSl_blrd9s34govabkLLkqPq1l.&amp;spm=a1z09.2.0.0.16022e8djmkhS9" xr:uid="{6FB9C11B-D844-4017-8FAE-7B9D33B02A74}"/>
+    <hyperlink ref="E19" r:id="rId11" display="https://detail.tmall.com/item.htm?abbucket=6&amp;id=599997955029&amp;pisk=g_FSJBgv_3x5MCbRv372fyTjpQGIVZ5aJegLSydyJbhJAvEafvPrayyBOkUTz0zUJ2FQYohEpgczOoZLAByzabkd9mZJTYPQ-BgLJkboYaX4rzcn9GSZO1zurRfUdZFSJqhYoVpJ2tkJDAvDLGSN_69vsmSCbz-EYGyx5VhKy0HJDZgISLhKe0dAl23e2Dn8vrQjm29pwXpJkK3K73hKyLCAM4uMyL3-9xCxm2hKvkhdljnmJXnLvXHpwhuC80a5RI-ZoeXt4znX9BFRtYisvpRBOS3SFWU-crz4G4MSXvZai2V80yFzZxj6XX44CkwLxOJmNye-wVzlNIGTy-PIuW7ed0EuGrFohFRZO8E7pA2fsdD-d0wYwxTp9rcxmAeQVg9o28rjIqHvR104bmUuw-_HDzEZVb3x31Q_kve4ZAVPDQGTIzlzpkXwnbaLejsz5Cos9NpBlAAIlc7flpvHQ1UCJ7KrBpk-o4GflZtSMY3mlc7flpvneq02hZ_XVjC..&amp;rn=617feaae5f94b5894f68d298b418e5fa&amp;spm=a1z10.5-b-s.w4011-25968523091.46.b6a0701d6EDwWY&amp;skuId=5973228525625" xr:uid="{E59FA095-5ED9-4AB6-A364-A1663E5F7967}"/>
+    <hyperlink ref="E20" r:id="rId12" display="https://item.taobao.com/item.htm?abbucket=8&amp;id=745548099223&amp;mi_id=00004OOG_NYymRcOUs8qQ4J16N7SfkKOrFY0K3XnxPj_dEs&amp;ns=1&amp;skuId=5310177214467&amp;spm=a21n57.1.hoverItem.2&amp;utparam=%7B%22aplus_abtest%22%3A%22d4a04f9cca5a6274e0629b42b0525f0d%22%7D&amp;xxc=taobaoSearch" xr:uid="{42F45CDB-86D2-44F7-A5BA-BEF4668BACD9}"/>
+    <hyperlink ref="E32" r:id="rId13" display="https://detail.tmall.com/item.htm?abbucket=6&amp;id=680012535670&amp;pisk=g0xjuU68YSVj0CDx6SkzOd_-JEI6lYoFMR69KdE4BiIxCcOWtNkDuou6PpASnGRwB1O6a_xqn1k01C96hZBABtn8e96b65E9BR69aiQMu15V1G9MOYlEYDJDnGbtTXoFPVtaTiBA6OQtBTBdQYWYJeyKYGjtTfazXZmCjIiagqyTyTClCoBAMCQ8wO1RHoB96_QRpOEAXGdtF_BchlEAXNe8e958W5IOXgQRLO4YWoItFLClBGC96ZHWe_XOX1H3EWWsQs9jCuy8KCoRDKC7XlKxjZ1Qe_BlU39lk6QRGlLyVt_f9KKKeo5Ve3-58ayZ-gpHzIB5A0zAvLT9Oedi8zjXBEdGPIcuP_8JmdCOzREeFp9vJgKZBJbWwO_dXawTXLscwN-AvDF5EUp2WnAbClBD0H71taMTjNSJYwLpGRDHeiB9swxZtofvBpxH8MizkMpWWBT14dEFOGHL58_3fT1EFYagSyopCAIABvhhkTXfVYM7GgQAET1EFYagSZBlUzMSFSsR.&amp;rn=231ec00e6e2790db3a6fd236d8bdbc94&amp;spm=a1z10.5-b.w4011-24399291437.54.78ac739ca5kPLK&amp;skuId=4875714089626" xr:uid="{58F62DF9-67CF-4905-8F70-77C15C8FD831}"/>
+    <hyperlink ref="E25" r:id="rId14" xr:uid="{EC25EA05-6DC9-4A87-9C36-32D903E88360}"/>
+    <hyperlink ref="E27" r:id="rId15" xr:uid="{2A053BBD-7322-4612-8A16-87449CD5652E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Structure/zh-CN/bom表.xlsx
+++ b/Structure/zh-CN/bom表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FINS实验室\FinsROV-An-Underwater-Camera-Based-Multi-Robot-Platform\Structure\zh-CN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23E3A8FE-2586-44D0-8AC1-663675A37C78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B93BE944-D205-48BC-83DE-19125A6AF103}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{880EE660-C71F-4428-A3AE-46F35EABC731}"/>
   </bookViews>
@@ -406,7 +406,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>无孔铝合金舱盖/半球罩+压板</t>
+    <t>无孔铝合金舱盖或者半球罩+压板</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -854,7 +854,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -966,6 +966,9 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1019,15 +1022,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1384,7 +1378,7 @@
       <c r="G1" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="46" t="s">
+      <c r="I1" s="47" t="s">
         <v>88</v>
       </c>
       <c r="J1" s="12" t="s">
@@ -1398,7 +1392,7 @@
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="53" t="s">
+      <c r="A2" s="54" t="s">
         <v>33</v>
       </c>
       <c r="B2" s="15" t="s">
@@ -1410,13 +1404,13 @@
       <c r="D2" s="15">
         <v>240</v>
       </c>
-      <c r="E2" s="50" t="s">
+      <c r="E2" s="51" t="s">
         <v>43</v>
       </c>
       <c r="F2" s="16"/>
       <c r="G2" s="17"/>
-      <c r="I2" s="46"/>
-      <c r="J2" s="42" t="s">
+      <c r="I2" s="47"/>
+      <c r="J2" s="43" t="s">
         <v>62</v>
       </c>
       <c r="K2" s="1" t="s">
@@ -1427,7 +1421,7 @@
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="54"/>
+      <c r="A3" s="55"/>
       <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
@@ -1437,11 +1431,11 @@
       <c r="D3" s="2">
         <v>180</v>
       </c>
-      <c r="E3" s="51"/>
+      <c r="E3" s="52"/>
       <c r="F3" s="3"/>
       <c r="G3" s="4"/>
-      <c r="I3" s="46"/>
-      <c r="J3" s="42"/>
+      <c r="I3" s="47"/>
+      <c r="J3" s="43"/>
       <c r="K3" s="2" t="s">
         <v>64</v>
       </c>
@@ -1450,7 +1444,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="54"/>
+      <c r="A4" s="55"/>
       <c r="B4" s="2" t="s">
         <v>8</v>
       </c>
@@ -1460,11 +1454,11 @@
       <c r="D4" s="2">
         <v>680</v>
       </c>
-      <c r="E4" s="51"/>
+      <c r="E4" s="52"/>
       <c r="F4" s="3"/>
       <c r="G4" s="4"/>
-      <c r="I4" s="46"/>
-      <c r="J4" s="43"/>
+      <c r="I4" s="47"/>
+      <c r="J4" s="44"/>
       <c r="K4" s="2" t="s">
         <v>65</v>
       </c>
@@ -1473,7 +1467,7 @@
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="54"/>
+      <c r="A5" s="55"/>
       <c r="B5" s="2" t="s">
         <v>9</v>
       </c>
@@ -1483,10 +1477,10 @@
       <c r="D5" s="2">
         <v>480</v>
       </c>
-      <c r="E5" s="51"/>
+      <c r="E5" s="52"/>
       <c r="F5" s="3"/>
       <c r="G5" s="4"/>
-      <c r="J5" s="44" t="s">
+      <c r="J5" s="45" t="s">
         <v>66</v>
       </c>
       <c r="K5" s="2" t="s">
@@ -1497,7 +1491,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="54"/>
+      <c r="A6" s="55"/>
       <c r="B6" s="2" t="s">
         <v>10</v>
       </c>
@@ -1507,10 +1501,10 @@
       <c r="D6" s="2">
         <v>1140</v>
       </c>
-      <c r="E6" s="52"/>
+      <c r="E6" s="53"/>
       <c r="F6" s="3"/>
       <c r="G6" s="4"/>
-      <c r="J6" s="42"/>
+      <c r="J6" s="43"/>
       <c r="K6" s="2" t="s">
         <v>68</v>
       </c>
@@ -1519,7 +1513,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="28" x14ac:dyDescent="0.3">
-      <c r="A7" s="54"/>
+      <c r="A7" s="55"/>
       <c r="B7" s="9" t="s">
         <v>45</v>
       </c>
@@ -1538,7 +1532,7 @@
       <c r="G7" s="36" t="s">
         <v>103</v>
       </c>
-      <c r="J7" s="42"/>
+      <c r="J7" s="43"/>
       <c r="K7" s="2" t="s">
         <v>69</v>
       </c>
@@ -1547,8 +1541,8 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="26" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="54"/>
-      <c r="B8" s="47" t="s">
+      <c r="A8" s="55"/>
+      <c r="B8" s="48" t="s">
         <v>18</v>
       </c>
       <c r="C8" s="2">
@@ -1564,7 +1558,7 @@
         <v>20</v>
       </c>
       <c r="G8" s="10"/>
-      <c r="J8" s="42"/>
+      <c r="J8" s="43"/>
       <c r="K8" s="2" t="s">
         <v>70</v>
       </c>
@@ -1573,8 +1567,8 @@
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="54"/>
-      <c r="B9" s="49"/>
+      <c r="A9" s="55"/>
+      <c r="B9" s="50"/>
       <c r="C9" s="2">
         <v>4</v>
       </c>
@@ -1586,7 +1580,7 @@
         <v>21</v>
       </c>
       <c r="G9" s="10"/>
-      <c r="J9" s="42"/>
+      <c r="J9" s="43"/>
       <c r="K9" s="2" t="s">
         <v>71</v>
       </c>
@@ -1595,7 +1589,7 @@
       </c>
     </row>
     <row r="10" spans="1:12" ht="28" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="54"/>
+      <c r="A10" s="55"/>
       <c r="B10" s="2" t="s">
         <v>38</v>
       </c>
@@ -1603,16 +1597,16 @@
         <v>1</v>
       </c>
       <c r="D10" s="2">
-        <v>515</v>
-      </c>
-      <c r="E10" s="58" t="s">
+        <v>370</v>
+      </c>
+      <c r="E10" s="56" t="s">
         <v>39</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>106</v>
       </c>
       <c r="G10" s="4"/>
-      <c r="J10" s="42"/>
+      <c r="J10" s="43"/>
       <c r="K10" s="2" t="s">
         <v>72</v>
       </c>
@@ -1621,27 +1615,27 @@
       </c>
     </row>
     <row r="11" spans="1:12" ht="26" x14ac:dyDescent="0.3">
-      <c r="A11" s="54"/>
-      <c r="B11" s="55" t="s">
+      <c r="A11" s="55"/>
+      <c r="B11" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="C11" s="55">
+      <c r="C11" s="5">
         <v>1</v>
       </c>
-      <c r="D11" s="55">
+      <c r="D11" s="5">
         <v>150</v>
       </c>
-      <c r="E11" s="59"/>
-      <c r="F11" s="56" t="s">
+      <c r="E11" s="57"/>
+      <c r="F11" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="G11" s="57"/>
-      <c r="J11" s="42"/>
+      <c r="G11" s="37"/>
+      <c r="J11" s="43"/>
       <c r="K11" s="2"/>
       <c r="L11" s="29"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" s="54"/>
+      <c r="A12" s="55"/>
       <c r="B12" s="5" t="s">
         <v>36</v>
       </c>
@@ -1652,7 +1646,7 @@
       </c>
       <c r="F12" s="6"/>
       <c r="G12" s="18"/>
-      <c r="J12" s="42"/>
+      <c r="J12" s="43"/>
       <c r="K12" s="2" t="s">
         <v>73</v>
       </c>
@@ -1661,7 +1655,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="28" x14ac:dyDescent="0.3">
-      <c r="A13" s="40" t="s">
+      <c r="A13" s="41" t="s">
         <v>11</v>
       </c>
       <c r="B13" s="2" t="s">
@@ -1682,7 +1676,7 @@
       <c r="G13" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="J13" s="43"/>
+      <c r="J13" s="44"/>
       <c r="K13" s="2" t="s">
         <v>74</v>
       </c>
@@ -1691,7 +1685,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="39" x14ac:dyDescent="0.3">
-      <c r="A14" s="40"/>
+      <c r="A14" s="41"/>
       <c r="B14" s="2" t="s">
         <v>15</v>
       </c>
@@ -1708,7 +1702,7 @@
         <v>17</v>
       </c>
       <c r="G14" s="18"/>
-      <c r="J14" s="44" t="s">
+      <c r="J14" s="45" t="s">
         <v>75</v>
       </c>
       <c r="K14" s="2" t="s">
@@ -1719,7 +1713,7 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="52" x14ac:dyDescent="0.3">
-      <c r="A15" s="40"/>
+      <c r="A15" s="41"/>
       <c r="B15" s="2" t="s">
         <v>22</v>
       </c>
@@ -1738,7 +1732,7 @@
       <c r="G15" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="J15" s="43"/>
+      <c r="J15" s="44"/>
       <c r="K15" s="2" t="s">
         <v>77</v>
       </c>
@@ -1747,7 +1741,7 @@
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" s="40"/>
+      <c r="A16" s="41"/>
       <c r="B16" s="2" t="s">
         <v>25</v>
       </c>
@@ -1764,7 +1758,7 @@
         <v>49</v>
       </c>
       <c r="G16" s="4"/>
-      <c r="J16" s="44" t="s">
+      <c r="J16" s="45" t="s">
         <v>78</v>
       </c>
       <c r="K16" s="2" t="s">
@@ -1775,7 +1769,7 @@
       </c>
     </row>
     <row r="17" spans="1:12" ht="28" x14ac:dyDescent="0.3">
-      <c r="A17" s="40"/>
+      <c r="A17" s="41"/>
       <c r="B17" s="2" t="s">
         <v>26</v>
       </c>
@@ -1792,7 +1786,7 @@
         <v>28</v>
       </c>
       <c r="G17" s="10"/>
-      <c r="J17" s="42"/>
+      <c r="J17" s="43"/>
       <c r="K17" s="2" t="s">
         <v>80</v>
       </c>
@@ -1801,7 +1795,7 @@
       </c>
     </row>
     <row r="18" spans="1:12" ht="28" x14ac:dyDescent="0.3">
-      <c r="A18" s="40"/>
+      <c r="A18" s="41"/>
       <c r="B18" s="2" t="s">
         <v>51</v>
       </c>
@@ -1816,7 +1810,7 @@
       </c>
       <c r="F18" s="3"/>
       <c r="G18" s="10"/>
-      <c r="J18" s="43"/>
+      <c r="J18" s="44"/>
       <c r="K18" s="2" t="s">
         <v>81</v>
       </c>
@@ -1825,7 +1819,7 @@
       </c>
     </row>
     <row r="19" spans="1:12" ht="28" x14ac:dyDescent="0.3">
-      <c r="A19" s="40"/>
+      <c r="A19" s="41"/>
       <c r="B19" s="2" t="s">
         <v>53</v>
       </c>
@@ -1853,7 +1847,7 @@
       </c>
     </row>
     <row r="20" spans="1:12" ht="28" x14ac:dyDescent="0.3">
-      <c r="A20" s="40"/>
+      <c r="A20" s="41"/>
       <c r="B20" s="2" t="s">
         <v>29</v>
       </c>
@@ -1881,7 +1875,7 @@
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A21" s="40"/>
+      <c r="A21" s="41"/>
       <c r="B21" s="2" t="s">
         <v>40</v>
       </c>
@@ -1896,7 +1890,7 @@
       </c>
       <c r="F21" s="3"/>
       <c r="G21" s="10"/>
-      <c r="J21" s="44" t="s">
+      <c r="J21" s="45" t="s">
         <v>85</v>
       </c>
       <c r="K21" s="2" t="s">
@@ -1907,7 +1901,7 @@
       </c>
     </row>
     <row r="22" spans="1:12" ht="28" x14ac:dyDescent="0.3">
-      <c r="A22" s="40"/>
+      <c r="A22" s="41"/>
       <c r="B22" s="2" t="s">
         <v>41</v>
       </c>
@@ -1919,7 +1913,7 @@
         <v>42</v>
       </c>
       <c r="G22" s="19"/>
-      <c r="J22" s="42"/>
+      <c r="J22" s="43"/>
       <c r="K22" s="2" t="s">
         <v>76</v>
       </c>
@@ -1928,7 +1922,7 @@
       </c>
     </row>
     <row r="23" spans="1:12" ht="42.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="40" t="s">
+      <c r="A23" s="41" t="s">
         <v>34</v>
       </c>
       <c r="B23" s="9" t="s">
@@ -1940,7 +1934,7 @@
         <v>102</v>
       </c>
       <c r="G23" s="19"/>
-      <c r="J23" s="45"/>
+      <c r="J23" s="46"/>
       <c r="K23" s="20" t="s">
         <v>87</v>
       </c>
@@ -1949,7 +1943,7 @@
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A24" s="40"/>
+      <c r="A24" s="41"/>
       <c r="B24" s="9" t="s">
         <v>61</v>
       </c>
@@ -1961,8 +1955,8 @@
       <c r="G24" s="19"/>
     </row>
     <row r="25" spans="1:12" ht="70" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="40"/>
-      <c r="B25" s="47" t="s">
+      <c r="A25" s="41"/>
+      <c r="B25" s="48" t="s">
         <v>90</v>
       </c>
       <c r="C25" s="5">
@@ -1971,7 +1965,7 @@
       <c r="D25" s="5">
         <v>25.2</v>
       </c>
-      <c r="E25" s="38" t="s">
+      <c r="E25" s="39" t="s">
         <v>94</v>
       </c>
       <c r="F25" s="24" t="s">
@@ -1980,30 +1974,30 @@
       <c r="G25" s="19"/>
     </row>
     <row r="26" spans="1:12" ht="28" x14ac:dyDescent="0.3">
-      <c r="A26" s="40"/>
-      <c r="B26" s="48"/>
+      <c r="A26" s="41"/>
+      <c r="B26" s="49"/>
       <c r="C26" s="5">
         <v>2</v>
       </c>
       <c r="D26" s="5">
         <v>12.6</v>
       </c>
-      <c r="E26" s="39"/>
+      <c r="E26" s="40"/>
       <c r="F26" s="24" t="s">
         <v>99</v>
       </c>
       <c r="G26" s="19"/>
     </row>
     <row r="27" spans="1:12" ht="28" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="40"/>
-      <c r="B27" s="48"/>
+      <c r="A27" s="41"/>
+      <c r="B27" s="49"/>
       <c r="C27" s="5">
         <v>2</v>
       </c>
       <c r="D27" s="5">
         <v>36</v>
       </c>
-      <c r="E27" s="38" t="s">
+      <c r="E27" s="39" t="s">
         <v>96</v>
       </c>
       <c r="F27" s="24" t="s">
@@ -2012,22 +2006,22 @@
       <c r="G27" s="19"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A28" s="40"/>
-      <c r="B28" s="49"/>
+      <c r="A28" s="41"/>
+      <c r="B28" s="50"/>
       <c r="C28" s="5">
         <v>1</v>
       </c>
       <c r="D28" s="5">
         <v>24</v>
       </c>
-      <c r="E28" s="39"/>
+      <c r="E28" s="40"/>
       <c r="F28" s="24" t="s">
         <v>98</v>
       </c>
       <c r="G28" s="19"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A29" s="40"/>
+      <c r="A29" s="41"/>
       <c r="B29" s="9" t="s">
         <v>91</v>
       </c>
@@ -2037,7 +2031,7 @@
       <c r="G29" s="19"/>
     </row>
     <row r="30" spans="1:12" ht="42" x14ac:dyDescent="0.3">
-      <c r="A30" s="40"/>
+      <c r="A30" s="41"/>
       <c r="B30" s="9" t="s">
         <v>92</v>
       </c>
@@ -2049,7 +2043,7 @@
       <c r="G30" s="19"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A31" s="40"/>
+      <c r="A31" s="41"/>
       <c r="B31" s="9" t="s">
         <v>60</v>
       </c>
@@ -2061,7 +2055,7 @@
       <c r="G31" s="19"/>
     </row>
     <row r="32" spans="1:12" ht="28.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="41"/>
+      <c r="A32" s="42"/>
       <c r="B32" s="20" t="s">
         <v>35</v>
       </c>
@@ -2078,15 +2072,15 @@
       <c r="G32" s="22"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="37" t="s">
+      <c r="A33" s="38" t="s">
         <v>104</v>
       </c>
-      <c r="B33" s="37"/>
-      <c r="C33" s="37"/>
-      <c r="D33" s="37"/>
-      <c r="E33" s="37"/>
-      <c r="F33" s="37"/>
-      <c r="G33" s="37"/>
+      <c r="B33" s="38"/>
+      <c r="C33" s="38"/>
+      <c r="D33" s="38"/>
+      <c r="E33" s="38"/>
+      <c r="F33" s="38"/>
+      <c r="G33" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="16">
